--- a/exports/trend_1d/MOTHERSON_full_report.xlsx
+++ b/exports/trend_1d/MOTHERSON_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42038</v>
+        <v>42039</v>
       </c>
       <c r="H2" t="n">
-        <v>52.73</v>
+        <v>51.47</v>
       </c>
       <c r="I2" t="n">
         <v>51.5282092143</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>0.44</v>
+        <v>-1.96</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>2.29</v>
       </c>
       <c r="M2" t="n">
         <v>0.9399999999999999</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>12.03</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42053</v>
+        <v>42054</v>
       </c>
       <c r="H3" t="n">
-        <v>54.17</v>
+        <v>56.73</v>
       </c>
       <c r="I3" t="n">
         <v>56.22887981246159</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.25</v>
+        <v>-10.22</v>
       </c>
       <c r="L3" t="n">
-        <v>8.41</v>
+        <v>10.55</v>
       </c>
       <c r="M3" t="n">
         <v>1.73</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.07</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42116</v>
+        <v>42117</v>
       </c>
       <c r="H4" t="n">
-        <v>57.6</v>
+        <v>56.4</v>
       </c>
       <c r="I4" t="n">
         <v>56.47894643672174</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K4" t="n">
-        <v>1.53</v>
+        <v>-0.58</v>
       </c>
       <c r="L4" t="n">
         <v>8.869999999999999</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.03</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42132</v>
+        <v>42135</v>
       </c>
       <c r="H5" t="n">
-        <v>57.23</v>
+        <v>60.3</v>
       </c>
       <c r="I5" t="n">
         <v>60.20178771172217</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.47</v>
+        <v>-6.91</v>
       </c>
       <c r="L5" t="n">
         <v>7.8</v>
@@ -726,7 +785,7 @@
         <v>5.73</v>
       </c>
       <c r="N5" t="n">
-        <v>5.19</v>
+        <v>5.36</v>
       </c>
       <c r="O5" t="n">
         <v>-2.08</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.77</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42223</v>
+        <v>42226</v>
       </c>
       <c r="H6" t="n">
-        <v>61.63</v>
+        <v>60.5</v>
       </c>
       <c r="I6" t="n">
         <v>60.90863636214257</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K6" t="n">
-        <v>2.21</v>
+        <v>0.33</v>
       </c>
       <c r="L6" t="n">
         <v>11.94</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>15.71</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H7" t="n">
-        <v>47.03</v>
+        <v>50.23</v>
       </c>
       <c r="I7" t="n">
         <v>48.14450705909217</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K7" t="n">
-        <v>22.26</v>
+        <v>16.98</v>
       </c>
       <c r="L7" t="n">
         <v>3.26</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>18.46</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H8" t="n">
-        <v>49.7</v>
+        <v>47.3</v>
       </c>
       <c r="I8" t="n">
         <v>47.81091347939051</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.06</v>
+        <v>-5.83</v>
       </c>
       <c r="L8" t="n">
         <v>9.359999999999999</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.72</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H9" t="n">
-        <v>43.23</v>
+        <v>44.17</v>
       </c>
       <c r="I9" t="n">
         <v>44.12948354355632</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K9" t="n">
-        <v>8.6</v>
+        <v>6.62</v>
       </c>
       <c r="L9" t="n">
         <v>4.44</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>16.13</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="H10" t="n">
-        <v>48.7</v>
+        <v>48.23</v>
       </c>
       <c r="I10" t="n">
         <v>48.33570793097352</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K10" t="n">
-        <v>10.26</v>
+        <v>9.19</v>
       </c>
       <c r="L10" t="n">
         <v>5.3</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>13.28</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42570</v>
+        <v>42571</v>
       </c>
       <c r="H11" t="n">
-        <v>53.37</v>
+        <v>54.6</v>
       </c>
       <c r="I11" t="n">
         <v>54.40750316238806</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.66</v>
+        <v>-13.21</v>
       </c>
       <c r="L11" t="n">
-        <v>13.06</v>
+        <v>14.24</v>
       </c>
       <c r="M11" t="n">
         <v>1.51</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>10.27</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42592</v>
+        <v>42593</v>
       </c>
       <c r="H12" t="n">
-        <v>58.23</v>
+        <v>55.97</v>
       </c>
       <c r="I12" t="n">
         <v>56.22412945129887</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>6.65</v>
+        <v>2.51</v>
       </c>
       <c r="L12" t="n">
         <v>1.89</v>
       </c>
       <c r="M12" t="n">
-        <v>-0</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
         <v>6.53</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>14.54</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42663</v>
+        <v>42664</v>
       </c>
       <c r="H13" t="n">
-        <v>58.37</v>
+        <v>59.07</v>
       </c>
       <c r="I13" t="n">
         <v>59.02347690573234</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.29</v>
+        <v>-5.54</v>
       </c>
       <c r="L13" t="n">
         <v>7.97</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>10.01</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42677</v>
+        <v>42678</v>
       </c>
       <c r="H14" t="n">
-        <v>55.5</v>
+        <v>53.37</v>
       </c>
       <c r="I14" t="n">
         <v>53.8894163780925</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.04</v>
+        <v>-9.65</v>
       </c>
       <c r="L14" t="n">
-        <v>6.94</v>
+        <v>10.33</v>
       </c>
       <c r="M14" t="n">
         <v>1.26</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>3.84</v>
       </c>
       <c r="O14" t="n">
         <v>1.2</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>11.39</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42740</v>
+        <v>42741</v>
       </c>
       <c r="H15" t="n">
-        <v>58.07</v>
+        <v>58.6</v>
       </c>
       <c r="I15" t="n">
         <v>58.51699645217674</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.81</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>11.11</v>
+        <v>11.73</v>
       </c>
       <c r="M15" t="n">
         <v>3.17</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.27</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42968</v>
+        <v>42969</v>
       </c>
       <c r="H16" t="n">
-        <v>84.93000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I16" t="n">
         <v>83.7644635380195</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K16" t="n">
-        <v>44.93</v>
+        <v>40.49</v>
       </c>
       <c r="L16" t="n">
         <v>3.19</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>12.78</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42996</v>
+        <v>42997</v>
       </c>
       <c r="H17" t="n">
-        <v>88.5</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>89.48223129349499</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.49</v>
+        <v>-9.84</v>
       </c>
       <c r="L17" t="n">
-        <v>9.4</v>
+        <v>10.37</v>
       </c>
       <c r="M17" t="n">
         <v>1.42</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43060</v>
+        <v>43061</v>
       </c>
       <c r="H18" t="n">
-        <v>93.5</v>
+        <v>91.33</v>
       </c>
       <c r="I18" t="n">
         <v>91.85579049693969</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K18" t="n">
-        <v>3.39</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>3.16</v>
@@ -1467,7 +1682,7 @@
         <v>1.23</v>
       </c>
       <c r="N18" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="O18" t="n">
         <v>2.18</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43076</v>
+        <v>43077</v>
       </c>
       <c r="H19" t="n">
-        <v>97.47</v>
+        <v>98.7</v>
       </c>
       <c r="I19" t="n">
         <v>98.18584187764884</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.72</v>
+        <v>-8.07</v>
       </c>
       <c r="L19" t="n">
-        <v>7.41</v>
+        <v>9.42</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>8.08</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H20" t="n">
-        <v>96.17</v>
+        <v>93.33</v>
       </c>
       <c r="I20" t="n">
         <v>95.24156967038941</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.56</v>
+        <v>-5.44</v>
       </c>
       <c r="L20" t="n">
-        <v>3.92</v>
+        <v>6.21</v>
       </c>
       <c r="M20" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
         <v>3.7</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H21" t="n">
-        <v>85.73</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I21" t="n">
         <v>88.07761668071038</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K21" t="n">
-        <v>8.140000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="L21" t="n">
         <v>5.65</v>
       </c>
       <c r="M21" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
         <v>4</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.52</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43236</v>
+        <v>43237</v>
       </c>
       <c r="H22" t="n">
-        <v>88.23</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>87.97573602449802</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K22" t="n">
-        <v>0.15</v>
+        <v>-0.57</v>
       </c>
       <c r="L22" t="n">
         <v>0.99</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.41</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43306</v>
+        <v>43307</v>
       </c>
       <c r="H23" t="n">
-        <v>79.33</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>81.59575008006243</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K23" t="n">
-        <v>9.44</v>
+        <v>6.47</v>
       </c>
       <c r="L23" t="n">
         <v>3.2</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43355</v>
+        <v>43357</v>
       </c>
       <c r="H24" t="n">
-        <v>77.03</v>
+        <v>76.47</v>
       </c>
       <c r="I24" t="n">
         <v>76.60491761957921</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.98</v>
+        <v>-6.66</v>
       </c>
       <c r="L24" t="n">
         <v>8.5</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.65</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43451</v>
+        <v>43452</v>
       </c>
       <c r="H25" t="n">
-        <v>66.7</v>
+        <v>68.67</v>
       </c>
       <c r="I25" t="n">
         <v>68.42285927269373</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K25" t="n">
-        <v>12.78</v>
+        <v>10.2</v>
       </c>
       <c r="L25" t="n">
         <v>2.82</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>16.57</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H26" t="n">
-        <v>59.97</v>
+        <v>57.77</v>
       </c>
       <c r="I26" t="n">
         <v>59.35094841526037</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>-12.67</v>
+        <v>-15.87</v>
       </c>
       <c r="L26" t="n">
-        <v>13.35</v>
+        <v>17.62</v>
       </c>
       <c r="M26" t="n">
         <v>1.6</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>13.03</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43518</v>
+        <v>43521</v>
       </c>
       <c r="H27" t="n">
-        <v>57.07</v>
+        <v>63.3</v>
       </c>
       <c r="I27" t="n">
         <v>58.6096667685424</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K27" t="n">
-        <v>1.21</v>
+        <v>-9.57</v>
       </c>
       <c r="L27" t="n">
-        <v>4.38</v>
+        <v>10.73</v>
       </c>
       <c r="M27" t="n">
         <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>5.74</v>
+        <v>10.92</v>
       </c>
       <c r="O27" t="n">
         <v>-3.67</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>17.45</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43544</v>
+        <v>43546</v>
       </c>
       <c r="H28" t="n">
-        <v>62.47</v>
+        <v>58.47</v>
       </c>
       <c r="I28" t="n">
         <v>59.08863702235663</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.31</v>
+        <v>-7.63</v>
       </c>
       <c r="L28" t="n">
         <v>9.84</v>
@@ -2037,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.74</v>
+        <v>6.4</v>
       </c>
       <c r="O28" t="n">
         <v>10.92</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.69</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H29" t="n">
-        <v>41.43</v>
+        <v>45.17</v>
       </c>
       <c r="I29" t="n">
         <v>43.44384912802033</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K29" t="n">
-        <v>29.14</v>
+        <v>22.75</v>
       </c>
       <c r="L29" t="n">
         <v>10.77</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>16.67</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43739</v>
+        <v>43741</v>
       </c>
       <c r="H30" t="n">
-        <v>41.37</v>
+        <v>39.5</v>
       </c>
       <c r="I30" t="n">
         <v>39.87065634439305</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
-        <v>-8.41</v>
+        <v>-12.55</v>
       </c>
       <c r="L30" t="n">
-        <v>11.07</v>
+        <v>13</v>
       </c>
       <c r="M30" t="n">
         <v>1.09</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>18.12</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43754</v>
+        <v>43755</v>
       </c>
       <c r="H31" t="n">
-        <v>39.53</v>
+        <v>43.47</v>
       </c>
       <c r="I31" t="n">
         <v>43.42905426334758</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.08</v>
+        <v>-10.05</v>
       </c>
       <c r="L31" t="n">
-        <v>5.32</v>
+        <v>12.73</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="O31" t="n">
         <v>-4.52</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>17.67</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H32" t="n">
-        <v>55.23</v>
+        <v>53.17</v>
       </c>
       <c r="I32" t="n">
         <v>54.37206236305448</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K32" t="n">
-        <v>27.05</v>
+        <v>22.31</v>
       </c>
       <c r="L32" t="n">
         <v>9.199999999999999</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.83</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43936</v>
+        <v>43937</v>
       </c>
       <c r="H33" t="n">
-        <v>28.3</v>
+        <v>32.43</v>
       </c>
       <c r="I33" t="n">
         <v>30.58996628714058</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K33" t="n">
-        <v>46.77</v>
+        <v>39.01</v>
       </c>
       <c r="L33" t="n">
         <v>4.95</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>34.68</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H34" t="n">
-        <v>46.37</v>
+        <v>43.63</v>
       </c>
       <c r="I34" t="n">
         <v>43.82526111791083</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K34" t="n">
-        <v>42.98</v>
+        <v>34.54</v>
       </c>
       <c r="L34" t="n">
         <v>13.35</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>17.11</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44141</v>
+        <v>44144</v>
       </c>
       <c r="H35" t="n">
-        <v>46.57</v>
+        <v>48.93</v>
       </c>
       <c r="I35" t="n">
         <v>47.38798488957164</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.74</v>
+        <v>-12.15</v>
       </c>
       <c r="L35" t="n">
         <v>14.6</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.33</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44216</v>
+        <v>44217</v>
       </c>
       <c r="H36" t="n">
-        <v>62.93</v>
+        <v>61.37</v>
       </c>
       <c r="I36" t="n">
         <v>61.60600802318453</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K36" t="n">
-        <v>28.61</v>
+        <v>25.42</v>
       </c>
       <c r="L36" t="n">
         <v>4.41</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>12.82</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44236</v>
+        <v>44237</v>
       </c>
       <c r="H37" t="n">
-        <v>64.27</v>
+        <v>69.23</v>
       </c>
       <c r="I37" t="n">
         <v>66.81228191528112</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.73</v>
+        <v>-12.81</v>
       </c>
       <c r="L37" t="n">
-        <v>7.27</v>
+        <v>14.55</v>
       </c>
       <c r="M37" t="n">
         <v>1.72</v>
       </c>
       <c r="N37" t="n">
-        <v>5.73</v>
+        <v>7.72</v>
       </c>
       <c r="O37" t="n">
         <v>-2.48</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>17.07</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H38" t="n">
-        <v>84.09999999999999</v>
+        <v>80.13</v>
       </c>
       <c r="I38" t="n">
         <v>80.33792642655804</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K38" t="n">
-        <v>21.48</v>
+        <v>15.74</v>
       </c>
       <c r="L38" t="n">
         <v>8.609999999999999</v>
@@ -2607,7 +3062,7 @@
         <v>2.66</v>
       </c>
       <c r="N38" t="n">
-        <v>3.69</v>
+        <v>4.72</v>
       </c>
       <c r="O38" t="n">
         <v>7.72</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>16.87</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H39" t="n">
-        <v>87.83</v>
+        <v>93.33</v>
       </c>
       <c r="I39" t="n">
         <v>90.89443364106043</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.609999999999999</v>
+        <v>-16.47</v>
       </c>
       <c r="L39" t="n">
-        <v>12.57</v>
+        <v>17.52</v>
       </c>
       <c r="M39" t="n">
         <v>1.84</v>
       </c>
       <c r="N39" t="n">
-        <v>5.43</v>
+        <v>6.26</v>
       </c>
       <c r="O39" t="n">
         <v>-4.72</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>14.76</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H40" t="n">
-        <v>91.83</v>
+        <v>88.77</v>
       </c>
       <c r="I40" t="n">
         <v>88.93901011667481</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.61</v>
+        <v>-4.89</v>
       </c>
       <c r="L40" t="n">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="M40" t="n">
         <v>2.09</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>13.43</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44453</v>
+        <v>44454</v>
       </c>
       <c r="H41" t="n">
-        <v>88.23</v>
+        <v>90.77</v>
       </c>
       <c r="I41" t="n">
         <v>89.56894190494393</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K41" t="n">
-        <v>0.61</v>
+        <v>-2.25</v>
       </c>
       <c r="L41" t="n">
         <v>6.26</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9</v>
+        <v>1.07</v>
       </c>
       <c r="N41" t="n">
         <v>4.44</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H42" t="n">
-        <v>91.37</v>
+        <v>88.77</v>
       </c>
       <c r="I42" t="n">
         <v>90.30628199033453</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K42" t="n">
-        <v>0.66</v>
+        <v>-2.2</v>
       </c>
       <c r="L42" t="n">
         <v>7.54</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>13.94</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44515</v>
+        <v>44516</v>
       </c>
       <c r="H43" t="n">
-        <v>93.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I43" t="n">
         <v>98.99079840719476</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.44</v>
+        <v>-11.97</v>
       </c>
       <c r="L43" t="n">
-        <v>11.86</v>
+        <v>14.12</v>
       </c>
       <c r="M43" t="n">
         <v>1.03</v>
       </c>
       <c r="N43" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="O43" t="n">
         <v>-2.85</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>14.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H44" t="n">
-        <v>91.97</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I44" t="n">
         <v>86.26007221278499</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>-7.47</v>
+        <v>-13.38</v>
       </c>
       <c r="L44" t="n">
-        <v>10.79</v>
+        <v>13.81</v>
       </c>
       <c r="M44" t="n">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
       <c r="N44" t="n">
-        <v>4.02</v>
+        <v>6.38</v>
       </c>
       <c r="O44" t="n">
         <v>6.2</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>17.5</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44566</v>
+        <v>44567</v>
       </c>
       <c r="H45" t="n">
-        <v>89.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I45" t="n">
         <v>91.45490040516577</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.48</v>
+        <v>-7.55</v>
       </c>
       <c r="L45" t="n">
-        <v>6.85</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>1.05</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>11.88</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44574</v>
+        <v>44575</v>
       </c>
       <c r="H46" t="n">
-        <v>93.37</v>
+        <v>82.47</v>
       </c>
       <c r="I46" t="n">
         <v>88.56493521999252</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>0.83</v>
+        <v>-10.94</v>
       </c>
       <c r="L46" t="n">
-        <v>5.08</v>
+        <v>12.34</v>
       </c>
       <c r="M46" t="n">
-        <v>0.48</v>
+        <v>7.22</v>
       </c>
       <c r="N46" t="n">
-        <v>3.54</v>
+        <v>11.67</v>
       </c>
       <c r="O46" t="n">
         <v>3.93</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>20.01</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H47" t="n">
-        <v>56.1</v>
+        <v>58.1</v>
       </c>
       <c r="I47" t="n">
         <v>58.05735641742606</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K47" t="n">
-        <v>31.98</v>
+        <v>29.55</v>
       </c>
       <c r="L47" t="n">
         <v>9.01</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>14.8</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H48" t="n">
-        <v>51.63</v>
+        <v>50.2</v>
       </c>
       <c r="I48" t="n">
         <v>50.36349847751049</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>-11.14</v>
+        <v>-13.6</v>
       </c>
       <c r="L48" t="n">
-        <v>12.17</v>
+        <v>14.34</v>
       </c>
       <c r="M48" t="n">
         <v>1.32</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>13.3</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44762</v>
+        <v>44763</v>
       </c>
       <c r="H49" t="n">
-        <v>56.23</v>
+        <v>59.77</v>
       </c>
       <c r="I49" t="n">
         <v>56.6632531642156</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K49" t="n">
-        <v>-12.01</v>
+        <v>-19.06</v>
       </c>
       <c r="L49" t="n">
-        <v>14.14</v>
+        <v>21.71</v>
       </c>
       <c r="M49" t="n">
         <v>1.34</v>
       </c>
       <c r="N49" t="n">
-        <v>5.38</v>
+        <v>6.3</v>
       </c>
       <c r="O49" t="n">
         <v>-2.77</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>11.43</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H50" t="n">
-        <v>54.1</v>
+        <v>52.5</v>
       </c>
       <c r="I50" t="n">
         <v>53.5287018941152</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K50" t="n">
-        <v>-9.49</v>
+        <v>-12.16</v>
       </c>
       <c r="L50" t="n">
-        <v>10.88</v>
+        <v>12.5</v>
       </c>
       <c r="M50" t="n">
         <v>2.29</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.6</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44874</v>
+        <v>44875</v>
       </c>
       <c r="H51" t="n">
-        <v>45.53</v>
+        <v>46.97</v>
       </c>
       <c r="I51" t="n">
         <v>46.60873878351047</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" t="n">
-        <v>13.28</v>
+        <v>10.53</v>
       </c>
       <c r="L51" t="n">
         <v>3.81</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.47</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H52" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I52" t="n">
         <v>46.07344228037169</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.36</v>
+        <v>-2.07</v>
       </c>
       <c r="L52" t="n">
         <v>3.92</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>9.52</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44921</v>
+        <v>44922</v>
       </c>
       <c r="H53" t="n">
-        <v>47.8</v>
+        <v>48.97</v>
       </c>
       <c r="I53" t="n">
         <v>48.8502701504393</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.91</v>
+        <v>-6.46</v>
       </c>
       <c r="L53" t="n">
-        <v>4.28</v>
+        <v>6.67</v>
       </c>
       <c r="M53" t="n">
         <v>0.58</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>10.53</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H54" t="n">
-        <v>48.43</v>
+        <v>47.73</v>
       </c>
       <c r="I54" t="n">
         <v>47.97865089176538</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.1</v>
+        <v>-2.53</v>
       </c>
       <c r="L54" t="n">
-        <v>2.39</v>
+        <v>4.29</v>
       </c>
       <c r="M54" t="n">
         <v>2.46</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44960</v>
+        <v>44963</v>
       </c>
       <c r="H55" t="n">
-        <v>50.6</v>
+        <v>52.4</v>
       </c>
       <c r="I55" t="n">
         <v>52.01180112590757</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.01</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>7.54</v>
+        <v>10.35</v>
       </c>
       <c r="M55" t="n">
         <v>0.55</v>
       </c>
       <c r="N55" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
         <v>-1.45</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>11.67</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45000</v>
+        <v>45001</v>
       </c>
       <c r="H56" t="n">
-        <v>51.2</v>
+        <v>45.67</v>
       </c>
       <c r="I56" t="n">
         <v>50.8356711362554</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.29</v>
+        <v>-12.84</v>
       </c>
       <c r="L56" t="n">
-        <v>4.2</v>
+        <v>15.97</v>
       </c>
       <c r="M56" t="n">
-        <v>1.16</v>
+        <v>7.17</v>
       </c>
       <c r="N56" t="n">
-        <v>4.86</v>
+        <v>10.8</v>
       </c>
       <c r="O56" t="n">
         <v>3.56</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>14.71</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45037</v>
+        <v>45040</v>
       </c>
       <c r="H57" t="n">
-        <v>46.7</v>
+        <v>47.23</v>
       </c>
       <c r="I57" t="n">
         <v>47.15728645984019</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.26</v>
+        <v>-3.42</v>
       </c>
       <c r="L57" t="n">
         <v>4.07</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.99</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="H58" t="n">
-        <v>63.83</v>
+        <v>61.83</v>
       </c>
       <c r="I58" t="n">
         <v>62.51764036271937</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K58" t="n">
-        <v>35.15</v>
+        <v>30.91</v>
       </c>
       <c r="L58" t="n">
         <v>2.18</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>7</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.34</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45212</v>
+        <v>45215</v>
       </c>
       <c r="H59" t="n">
-        <v>62.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I59" t="n">
         <v>64.78339507464396</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.73</v>
+        <v>-4.97</v>
       </c>
       <c r="L59" t="n">
-        <v>3.78</v>
+        <v>5.29</v>
       </c>
       <c r="M59" t="n">
-        <v>0.59</v>
+        <v>1.38</v>
       </c>
       <c r="N59" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="O59" t="n">
         <v>-3.13</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.31</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H60" t="n">
-        <v>61.33</v>
+        <v>60.4</v>
       </c>
       <c r="I60" t="n">
         <v>60.76107024813614</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.5</v>
+        <v>-6.93</v>
       </c>
       <c r="L60" t="n">
         <v>8.890000000000001</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="H61" t="n">
-        <v>62.23</v>
+        <v>63.33</v>
       </c>
       <c r="I61" t="n">
         <v>62.63570269272153</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.03</v>
+        <v>-4.85</v>
       </c>
       <c r="L61" t="n">
-        <v>4.85</v>
+        <v>5.35</v>
       </c>
       <c r="M61" t="n">
         <v>2.04</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.4</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H62" t="n">
-        <v>77.33</v>
+        <v>73.47</v>
       </c>
       <c r="I62" t="n">
         <v>74.66231181515762</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K62" t="n">
-        <v>22.11</v>
+        <v>16.01</v>
       </c>
       <c r="L62" t="n">
         <v>5.05</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>13.4</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45397</v>
+        <v>45398</v>
       </c>
       <c r="H63" t="n">
-        <v>80.53</v>
+        <v>82.83</v>
       </c>
       <c r="I63" t="n">
         <v>82.15178697512304</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K63" t="n">
-        <v>-9.609999999999999</v>
+        <v>-12.74</v>
       </c>
       <c r="L63" t="n">
-        <v>11.88</v>
+        <v>14.06</v>
       </c>
       <c r="M63" t="n">
         <v>1.31</v>
       </c>
       <c r="N63" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="O63" t="n">
         <v>-4.99</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>10.8</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H64" t="n">
-        <v>128.83</v>
+        <v>117.01</v>
       </c>
       <c r="I64" t="n">
         <v>124.2882618221906</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K64" t="n">
-        <v>55.54</v>
+        <v>41.27</v>
       </c>
       <c r="L64" t="n">
         <v>4.83</v>
       </c>
       <c r="M64" t="n">
-        <v>2.11</v>
+        <v>2.72</v>
       </c>
       <c r="N64" t="n">
-        <v>5.93</v>
+        <v>9.17</v>
       </c>
       <c r="O64" t="n">
         <v>2.86</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>14.75</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45552</v>
+        <v>45553</v>
       </c>
       <c r="H65" t="n">
-        <v>130.01</v>
+        <v>136.11</v>
       </c>
       <c r="I65" t="n">
         <v>133.5896380141958</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K65" t="n">
-        <v>-11.11</v>
+        <v>-16.32</v>
       </c>
       <c r="L65" t="n">
-        <v>14.43</v>
+        <v>18.85</v>
       </c>
       <c r="M65" t="n">
         <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>3.17</v>
+        <v>4.69</v>
       </c>
       <c r="O65" t="n">
         <v>-9.17</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>10.8</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H66" t="n">
-        <v>132.91</v>
+        <v>128.99</v>
       </c>
       <c r="I66" t="n">
         <v>130.9270607034647</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.35</v>
+        <v>-5.23</v>
       </c>
       <c r="L66" t="n">
-        <v>4.47</v>
+        <v>5.58</v>
       </c>
       <c r="M66" t="n">
         <v>4.39</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>12.3</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H67" t="n">
-        <v>87.56</v>
+        <v>89.33</v>
       </c>
       <c r="I67" t="n">
         <v>88.26570425878487</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K67" t="n">
-        <v>32.12</v>
+        <v>30.75</v>
       </c>
       <c r="L67" t="n">
         <v>3.98</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>6</v>
+      </c>
+      <c r="U67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>9.98</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H68" t="n">
-        <v>85.95999999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="I68" t="n">
         <v>80.69836922020005</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.77</v>
+        <v>-11.24</v>
       </c>
       <c r="L68" t="n">
-        <v>6.92</v>
+        <v>12.02</v>
       </c>
       <c r="M68" t="n">
         <v>3.28</v>
       </c>
       <c r="N68" t="n">
-        <v>2.48</v>
+        <v>7.76</v>
       </c>
       <c r="O68" t="n">
         <v>2.02</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>17.31</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H69" t="n">
-        <v>85.56</v>
+        <v>86.45</v>
       </c>
       <c r="I69" t="n">
         <v>86.19178349692289</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K69" t="n">
-        <v>-7.91</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L69" t="n">
         <v>9.35</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>14.82</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H70" t="n">
-        <v>100.81</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="I70" t="n">
         <v>98.4713889312595</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K70" t="n">
-        <v>16.61</v>
+        <v>12.48</v>
       </c>
       <c r="L70" t="n">
         <v>2.17</v>
@@ -4431,7 +5270,7 @@
         <v>3.37</v>
       </c>
       <c r="N70" t="n">
-        <v>2.72</v>
+        <v>3.54</v>
       </c>
       <c r="O70" t="n">
         <v>1.04</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>9.67</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="H71" t="n">
-        <v>94.08</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I71" t="n">
         <v>99.11375784085773</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K71" t="n">
-        <v>3.25</v>
+        <v>-2.22</v>
       </c>
       <c r="L71" t="n">
         <v>6.69</v>
@@ -4488,7 +5339,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N71" t="n">
-        <v>4.27</v>
+        <v>5.65</v>
       </c>
       <c r="O71" t="n">
         <v>-3.54</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>12.06</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="H72" t="n">
-        <v>104.12</v>
+        <v>101.64</v>
       </c>
       <c r="I72" t="n">
         <v>102.505848388369</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K72" t="n">
-        <v>4.75</v>
+        <v>2.25</v>
       </c>
       <c r="L72" t="n">
         <v>8.35</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>9.4</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="H73" t="n">
-        <v>108.96</v>
+        <v>112.16</v>
       </c>
       <c r="I73" t="n">
         <v>110.4961803978715</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K73" t="n">
-        <v>-7.2</v>
+        <v>-10.35</v>
       </c>
       <c r="L73" t="n">
         <v>11.64</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H74" t="n">
-        <v>118.11</v>
+        <v>115.64</v>
       </c>
       <c r="I74" t="n">
         <v>115.7614244775069</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K74" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="L74" t="n">
         <v>3.31</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>7.36</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H75" t="n">
-        <v>114.09</v>
+        <v>121.32</v>
       </c>
       <c r="I75" t="n">
         <v>118.6773436028215</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K75" t="n">
-        <v>1.34</v>
+        <v>-4.91</v>
       </c>
       <c r="L75" t="n">
-        <v>2.12</v>
+        <v>8.52</v>
       </c>
       <c r="M75" t="n">
-        <v>1.7</v>
+        <v>8.68</v>
       </c>
       <c r="N75" t="n">
-        <v>2.2</v>
+        <v>6.34</v>
       </c>
       <c r="O75" t="n">
         <v>-2.09</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>10.01</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H76" t="n">
-        <v>128.65</v>
+        <v>122.88</v>
       </c>
       <c r="I76" t="n">
         <v>123.5195194331903</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K76" t="n">
-        <v>6.04</v>
+        <v>1.29</v>
       </c>
       <c r="L76" t="n">
         <v>4.34</v>
@@ -4773,7 +5684,7 @@
         <v>5.35</v>
       </c>
       <c r="N76" t="n">
-        <v>3.52</v>
+        <v>4.49</v>
       </c>
       <c r="O76" t="n">
         <v>6.34</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>11.4</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H77" t="n">
-        <v>116.9</v>
+        <v>122.16</v>
       </c>
       <c r="I77" t="n">
         <v>119.5116216623611</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K77" t="n">
-        <v>4.87</v>
+        <v>0.59</v>
       </c>
       <c r="L77" t="n">
         <v>3.59</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>14.86</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H78" t="n">
-        <v>164.45</v>
+        <v>158.15</v>
       </c>
       <c r="I78" t="n">
         <v>158.4841944536909</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K78" t="n">
-        <v>34.62</v>
+        <v>29.46</v>
       </c>
       <c r="L78" t="n">
         <v>4.22</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>6</v>
+      </c>
+      <c r="U78" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>30</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.8</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -9965,7 +10920,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -9975,7 +10930,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -9985,7 +10940,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.4</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="14">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.86</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.39</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.27</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55.54</v>
+        <v>41.27</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.1</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.98</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.69</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="21">
@@ -10065,7 +11020,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.6</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="22">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="27">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
